--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{288E95C5-6D0E-4C3D-90F7-182ADF911A56}"/>
+  <xr:revisionPtr revIDLastSave="110" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13EB87C8-57A8-40A3-A300-06201DC18695}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -209,6 +209,63 @@
   </si>
   <si>
     <t>A tiresome day with no break between classes.</t>
+  </si>
+  <si>
+    <t>13.08.2026</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>14.08.2026</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>15.08.2026</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>feeling good</t>
+  </si>
+  <si>
+    <t>16.08.2026</t>
+  </si>
+  <si>
+    <t>fun day</t>
+  </si>
+  <si>
+    <t>17.08.2026</t>
+  </si>
+  <si>
+    <t>tired</t>
+  </si>
+  <si>
+    <t>18.08.2026</t>
+  </si>
+  <si>
+    <t>feeling sleepy</t>
+  </si>
+  <si>
+    <t>19.08.2026</t>
+  </si>
+  <si>
+    <t>too much classes</t>
+  </si>
+  <si>
+    <t>20.08.2026</t>
+  </si>
+  <si>
+    <t>A good day</t>
   </si>
 </sst>
 </file>
@@ -489,6 +546,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1034,180 +1095,368 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+      <c r="A7" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="14">
+        <v>420</v>
+      </c>
+      <c r="C7" s="14">
+        <v>30</v>
+      </c>
+      <c r="D7" s="14">
+        <v>90</v>
+      </c>
+      <c r="E7" s="14">
+        <v>60</v>
+      </c>
+      <c r="F7" s="14">
+        <v>200</v>
+      </c>
+      <c r="G7" s="14">
+        <v>4</v>
+      </c>
+      <c r="H7" s="14">
+        <v>30</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
+        <v>610</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N7" s="17"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="14">
+        <v>480</v>
+      </c>
+      <c r="C8" s="14">
+        <v>30</v>
+      </c>
+      <c r="D8" s="14">
+        <v>120</v>
+      </c>
+      <c r="E8" s="14">
+        <v>60</v>
+      </c>
+      <c r="F8" s="14">
+        <v>250</v>
+      </c>
+      <c r="G8" s="14">
+        <v>5</v>
+      </c>
+      <c r="H8" s="14">
+        <v>30</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
+        <v>470</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="14">
+        <v>480</v>
+      </c>
+      <c r="C9" s="14">
+        <v>30</v>
+      </c>
+      <c r="D9" s="14">
+        <v>180</v>
+      </c>
+      <c r="E9" s="14">
+        <v>120</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14">
+        <v>120</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="14">
+        <v>480</v>
+      </c>
+      <c r="C10" s="14">
+        <v>30</v>
+      </c>
+      <c r="D10" s="14">
+        <v>180</v>
+      </c>
+      <c r="E10" s="14">
+        <v>120</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14">
+        <v>120</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="14">
+        <v>420</v>
+      </c>
+      <c r="C11" s="14">
+        <v>30</v>
+      </c>
+      <c r="D11" s="14">
+        <v>120</v>
+      </c>
+      <c r="E11" s="14">
+        <v>60</v>
+      </c>
+      <c r="F11" s="14">
+        <v>250</v>
+      </c>
+      <c r="G11" s="14">
+        <v>5</v>
+      </c>
+      <c r="H11" s="14">
+        <v>30</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="14">
+        <v>420</v>
+      </c>
+      <c r="C12" s="14">
+        <v>30</v>
+      </c>
+      <c r="D12" s="14">
+        <v>90</v>
+      </c>
+      <c r="E12" s="14">
+        <v>60</v>
+      </c>
+      <c r="F12" s="14">
+        <v>300</v>
+      </c>
+      <c r="G12" s="14">
+        <v>6</v>
+      </c>
+      <c r="H12" s="14">
+        <v>30</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="14">
+        <v>450</v>
+      </c>
+      <c r="C13" s="14">
+        <v>30</v>
+      </c>
+      <c r="D13" s="14">
+        <v>90</v>
+      </c>
+      <c r="E13" s="14">
+        <v>60</v>
+      </c>
+      <c r="F13" s="14">
+        <v>350</v>
+      </c>
+      <c r="G13" s="14">
+        <v>7</v>
+      </c>
+      <c r="H13" s="14">
+        <v>30</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="14">
+        <v>450</v>
+      </c>
+      <c r="C14" s="14">
+        <v>30</v>
+      </c>
+      <c r="D14" s="14">
+        <v>90</v>
+      </c>
+      <c r="E14" s="14">
+        <v>60</v>
+      </c>
+      <c r="F14" s="14">
+        <v>200</v>
+      </c>
+      <c r="G14" s="14">
+        <v>4</v>
+      </c>
+      <c r="H14" s="14">
+        <v>30</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>580</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="110" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13EB87C8-57A8-40A3-A300-06201DC18695}"/>
+  <xr:revisionPtr revIDLastSave="122" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{179594B7-F751-4C21-B5C4-0DA56485BE5F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -266,6 +266,15 @@
   </si>
   <si>
     <t>A good day</t>
+  </si>
+  <si>
+    <t>21.08.2026</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>stressed</t>
   </si>
 </sst>
 </file>
@@ -1459,26 +1468,50 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="14">
+        <v>480</v>
+      </c>
+      <c r="C15" s="14">
+        <v>30</v>
+      </c>
+      <c r="D15" s="14">
+        <v>90</v>
+      </c>
+      <c r="E15" s="14">
+        <v>60</v>
+      </c>
+      <c r="F15" s="14">
+        <v>250</v>
+      </c>
+      <c r="G15" s="14">
+        <v>5</v>
+      </c>
+      <c r="H15" s="14">
+        <v>30</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="122" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{179594B7-F751-4C21-B5C4-0DA56485BE5F}"/>
+  <xr:revisionPtr revIDLastSave="137" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36D3B1F0-1558-4C63-A672-62C52959B44C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -275,6 +275,12 @@
   </si>
   <si>
     <t>stressed</t>
+  </si>
+  <si>
+    <t>22.08.2026</t>
+  </si>
+  <si>
+    <t>relaxed</t>
   </si>
 </sst>
 </file>
@@ -1514,26 +1520,50 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="14">
+        <v>480</v>
+      </c>
+      <c r="C16" s="14">
+        <v>30</v>
+      </c>
+      <c r="D16" s="14">
+        <v>180</v>
+      </c>
+      <c r="E16" s="14">
+        <v>90</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>120</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="137" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36D3B1F0-1558-4C63-A672-62C52959B44C}"/>
+  <xr:revisionPtr revIDLastSave="149" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4643B13-ADDD-4CA8-92A2-FF516409C148}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>relaxed</t>
+  </si>
+  <si>
+    <t>23.08.2026</t>
   </si>
 </sst>
 </file>
@@ -1566,26 +1569,50 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="14">
+        <v>480</v>
+      </c>
+      <c r="C17" s="14">
+        <v>30</v>
+      </c>
+      <c r="D17" s="14">
+        <v>180</v>
+      </c>
+      <c r="E17" s="14">
+        <v>90</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>120</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="149" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4643B13-ADDD-4CA8-92A2-FF516409C148}"/>
+  <xr:revisionPtr revIDLastSave="173" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CAC14C3-CC55-47A5-ABF7-2F63B5E0B3E2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -284,6 +284,15 @@
   </si>
   <si>
     <t>23.08.2026</t>
+  </si>
+  <si>
+    <t>24.08.2026</t>
+  </si>
+  <si>
+    <t>25.08.2026</t>
+  </si>
+  <si>
+    <t>tired attending classes</t>
   </si>
 </sst>
 </file>
@@ -1615,48 +1624,96 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" s="14">
+        <v>420</v>
+      </c>
+      <c r="C18" s="14">
+        <v>30</v>
+      </c>
+      <c r="D18" s="14">
+        <v>90</v>
+      </c>
+      <c r="E18" s="14">
+        <v>60</v>
+      </c>
+      <c r="F18" s="14">
+        <v>250</v>
+      </c>
+      <c r="G18" s="14">
+        <v>5</v>
+      </c>
+      <c r="H18" s="14">
+        <v>30</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" s="14">
+        <v>420</v>
+      </c>
+      <c r="C19" s="14">
+        <v>30</v>
+      </c>
+      <c r="D19" s="14">
+        <v>90</v>
+      </c>
+      <c r="E19" s="14">
+        <v>60</v>
+      </c>
+      <c r="F19" s="14">
+        <v>350</v>
+      </c>
+      <c r="G19" s="14">
+        <v>7</v>
+      </c>
+      <c r="H19" s="14">
+        <v>30</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>460</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="173" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CAC14C3-CC55-47A5-ABF7-2F63B5E0B3E2}"/>
+  <xr:revisionPtr revIDLastSave="201" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFFF2DF8-5128-495E-A359-235496CF4331}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -293,6 +293,15 @@
   </si>
   <si>
     <t>tired attending classes</t>
+  </si>
+  <si>
+    <t>26.08.2026</t>
+  </si>
+  <si>
+    <t>27.08.2026</t>
+  </si>
+  <si>
+    <t>tired attending classes with no breaks.</t>
   </si>
 </sst>
 </file>
@@ -1716,48 +1725,94 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" s="14">
+        <v>420</v>
+      </c>
+      <c r="C20" s="14">
+        <v>30</v>
+      </c>
+      <c r="D20" s="14">
+        <v>90</v>
+      </c>
+      <c r="E20" s="14">
+        <v>60</v>
+      </c>
+      <c r="F20" s="14">
+        <v>300</v>
+      </c>
+      <c r="G20" s="14">
+        <v>6</v>
+      </c>
+      <c r="H20" s="14">
+        <v>30</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
+        <v>510</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N20" s="17"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+    <row r="21" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
+      <c r="C21" s="14">
+        <v>30</v>
+      </c>
+      <c r="D21" s="14">
+        <v>90</v>
+      </c>
+      <c r="E21" s="14">
+        <v>60</v>
+      </c>
+      <c r="F21" s="14">
+        <v>250</v>
+      </c>
+      <c r="G21" s="14">
+        <v>5</v>
+      </c>
+      <c r="H21" s="14">
+        <v>30</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="201" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFFF2DF8-5128-495E-A359-235496CF4331}"/>
+  <xr:revisionPtr revIDLastSave="212" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{454F9AFC-7BA1-4C9F-B3F9-8EE5B99BF506}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -302,6 +302,9 @@
   </si>
   <si>
     <t>tired attending classes with no breaks.</t>
+  </si>
+  <si>
+    <t>28.09.2026</t>
   </si>
 </sst>
 </file>
@@ -1815,25 +1818,47 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" s="14">
+        <v>420</v>
+      </c>
+      <c r="C22" s="14">
+        <v>30</v>
+      </c>
+      <c r="D22" s="14">
+        <v>90</v>
+      </c>
+      <c r="E22" s="14">
+        <v>60</v>
+      </c>
+      <c r="F22" s="14">
+        <v>300</v>
+      </c>
+      <c r="G22" s="14">
+        <v>6</v>
+      </c>
+      <c r="H22" s="14">
+        <v>30</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
+        <v>510</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="212" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{454F9AFC-7BA1-4C9F-B3F9-8EE5B99BF506}"/>
+  <xr:revisionPtr revIDLastSave="225" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{611DCB98-5E49-47DE-AB39-2BFF05859CD7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -305,6 +305,12 @@
   </si>
   <si>
     <t>28.09.2026</t>
+  </si>
+  <si>
+    <t>29.09.2026</t>
+  </si>
+  <si>
+    <t>finally weekend</t>
   </si>
 </sst>
 </file>
@@ -1862,26 +1868,48 @@
       <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
+      <c r="A23" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" s="14">
+        <v>420</v>
+      </c>
+      <c r="C23" s="14">
+        <v>30</v>
+      </c>
+      <c r="D23" s="14">
+        <v>120</v>
+      </c>
+      <c r="E23" s="14">
+        <v>120</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0</v>
+      </c>
+      <c r="G23" s="14">
+        <v>0</v>
+      </c>
       <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>750</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="225" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{611DCB98-5E49-47DE-AB39-2BFF05859CD7}"/>
+  <xr:revisionPtr revIDLastSave="243" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78B41E13-1047-4AB7-B3AA-8A31246DC9CF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="94">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -304,13 +304,19 @@
     <t>tired attending classes with no breaks.</t>
   </si>
   <si>
-    <t>28.09.2026</t>
+    <t>finally weekend</t>
   </si>
   <si>
-    <t>29.09.2026</t>
+    <t>28.08.2026</t>
   </si>
   <si>
-    <t>finally weekend</t>
+    <t>29.08.2026</t>
+  </si>
+  <si>
+    <t>30.08.2026</t>
+  </si>
+  <si>
+    <t>Sunday!!</t>
   </si>
 </sst>
 </file>
@@ -1825,7 +1831,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B22" s="14">
         <v>420</v>
@@ -1869,7 +1875,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B23" s="14">
         <v>420</v>
@@ -1889,14 +1895,16 @@
       <c r="G23" s="14">
         <v>0</v>
       </c>
-      <c r="H23" s="14"/>
+      <c r="H23" s="14">
+        <v>30</v>
+      </c>
       <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v>690</v>
+        <v>720</v>
       </c>
       <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="K23" s="16" t="s">
         <v>63</v>
@@ -1908,30 +1916,54 @@
         <v>65</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="14">
+        <v>480</v>
+      </c>
+      <c r="C24" s="14">
+        <v>30</v>
+      </c>
+      <c r="D24" s="14">
+        <v>240</v>
+      </c>
+      <c r="E24" s="14">
+        <v>120</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14">
+        <v>30</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="243" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78B41E13-1047-4AB7-B3AA-8A31246DC9CF}"/>
+  <xr:revisionPtr revIDLastSave="255" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E298E175-DE01-47D3-94D8-B4EB9460D423}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -318,6 +318,12 @@
   <si>
     <t>Sunday!!</t>
   </si>
+  <si>
+    <t>31.08.2026</t>
+  </si>
+  <si>
+    <t>busy day!</t>
+  </si>
 </sst>
 </file>
 
@@ -597,10 +603,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1966,26 +1968,50 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B25" s="14">
+        <v>420</v>
+      </c>
+      <c r="C25" s="14">
+        <v>30</v>
+      </c>
+      <c r="D25" s="14">
+        <v>90</v>
+      </c>
+      <c r="E25" s="14">
+        <v>60</v>
+      </c>
+      <c r="F25" s="14">
+        <v>250</v>
+      </c>
+      <c r="G25" s="14">
+        <v>6</v>
+      </c>
+      <c r="H25" s="14">
+        <v>30</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="255" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E298E175-DE01-47D3-94D8-B4EB9460D423}"/>
+  <xr:revisionPtr revIDLastSave="267" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFD1ADB1-C853-4629-B077-4FEC7335B3AB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -324,6 +324,12 @@
   <si>
     <t>busy day!</t>
   </si>
+  <si>
+    <t>1.09.2026</t>
+  </si>
+  <si>
+    <t>seven classes a dayy</t>
+  </si>
 </sst>
 </file>
 
@@ -603,6 +609,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2014,26 +2024,50 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" s="14">
+        <v>420</v>
+      </c>
+      <c r="C26" s="14">
+        <v>30</v>
+      </c>
+      <c r="D26" s="14">
+        <v>60</v>
+      </c>
+      <c r="E26" s="14">
+        <v>60</v>
+      </c>
+      <c r="F26" s="14">
+        <v>350</v>
+      </c>
+      <c r="G26" s="14">
+        <v>7</v>
+      </c>
+      <c r="H26" s="14">
+        <v>30</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="267" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFD1ADB1-C853-4629-B077-4FEC7335B3AB}"/>
+  <xr:revisionPtr revIDLastSave="279" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4763FAEB-C9C5-4279-999E-B7C33C8EF5F2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -329,6 +329,12 @@
   </si>
   <si>
     <t>seven classes a dayy</t>
+  </si>
+  <si>
+    <t>2.09.2026</t>
+  </si>
+  <si>
+    <t>getting used to it!</t>
   </si>
 </sst>
 </file>
@@ -2070,26 +2076,50 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B27" s="14">
+        <v>420</v>
+      </c>
+      <c r="C27" s="14">
+        <v>30</v>
+      </c>
+      <c r="D27" s="14">
+        <v>60</v>
+      </c>
+      <c r="E27" s="14">
+        <v>60</v>
+      </c>
+      <c r="F27" s="14">
+        <v>250</v>
+      </c>
+      <c r="G27" s="14">
+        <v>5</v>
+      </c>
+      <c r="H27" s="14">
+        <v>30</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>590</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="279" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4763FAEB-C9C5-4279-999E-B7C33C8EF5F2}"/>
+  <xr:revisionPtr revIDLastSave="292" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E394B1F-43DE-4C0F-A613-428C1090834F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -336,6 +336,12 @@
   <si>
     <t>getting used to it!</t>
   </si>
+  <si>
+    <t>3.09.2026</t>
+  </si>
+  <si>
+    <t>feeling good!</t>
+  </si>
 </sst>
 </file>
 
@@ -615,10 +621,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2122,26 +2124,50 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B28" s="14">
+        <v>420</v>
+      </c>
+      <c r="C28" s="14">
+        <v>30</v>
+      </c>
+      <c r="D28" s="14">
+        <v>60</v>
+      </c>
+      <c r="E28" s="14">
+        <v>60</v>
+      </c>
+      <c r="F28" s="14">
+        <v>150</v>
+      </c>
+      <c r="G28" s="14">
+        <v>3</v>
+      </c>
+      <c r="H28" s="14">
+        <v>30</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>690</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="13"/>

--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="292" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E394B1F-43DE-4C0F-A613-428C1090834F}"/>
+  <xr:revisionPtr revIDLastSave="304" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83FE1B61-ABDE-4FE4-8B7D-039CBBDA118D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="104">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -342,6 +342,12 @@
   <si>
     <t>feeling good!</t>
   </si>
+  <si>
+    <t>4.09.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> satisfied!</t>
+  </si>
 </sst>
 </file>
 
@@ -621,6 +627,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2170,26 +2180,50 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" s="14">
+        <v>420</v>
+      </c>
+      <c r="C29" s="14">
+        <v>30</v>
+      </c>
+      <c r="D29" s="14">
+        <v>60</v>
+      </c>
+      <c r="E29" s="14">
+        <v>60</v>
+      </c>
+      <c r="F29" s="14">
+        <v>250</v>
+      </c>
+      <c r="G29" s="14">
+        <v>5</v>
+      </c>
+      <c r="H29" s="14">
+        <v>30</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>590</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="13"/>
@@ -10404,6 +10438,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/12624870.xlsx
+++ b/12624870.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92cff096416d61ea/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="304" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83FE1B61-ABDE-4FE4-8B7D-039CBBDA118D}"/>
+  <xr:revisionPtr revIDLastSave="316" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B68AE126-7A41-4C27-8DF4-72FF84AC8D71}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="106">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -347,6 +347,12 @@
   </si>
   <si>
     <t xml:space="preserve"> satisfied!</t>
+  </si>
+  <si>
+    <t>5.09.2026</t>
+  </si>
+  <si>
+    <t>tired!</t>
   </si>
 </sst>
 </file>
@@ -627,10 +633,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2226,26 +2228,50 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="B30" s="14">
+        <v>420</v>
+      </c>
+      <c r="C30" s="14">
+        <v>30</v>
+      </c>
+      <c r="D30" s="14">
+        <v>60</v>
+      </c>
+      <c r="E30" s="14">
+        <v>60</v>
+      </c>
+      <c r="F30" s="14">
+        <v>50</v>
+      </c>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="14">
+        <v>90</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>710</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>730</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="13"/>
